--- a/сайт_записей_на_услуги.xlsx
+++ b/сайт_записей_на_услуги.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>Админ-панель:</t>
   </si>
@@ -66,9 +66,6 @@
     <t>Создание "окошек" по времени для записи</t>
   </si>
   <si>
-    <t>Страницы "О нас", "FAQ"</t>
-  </si>
-  <si>
     <t>Описание задачи</t>
   </si>
   <si>
@@ -87,9 +84,6 @@
     <t>Страница с формой записи (почта, имя, примечание)</t>
   </si>
   <si>
-    <t>Редактирование FAQ</t>
-  </si>
-  <si>
     <t>Страница поиска (в т.ч. векторный поиск и поиск по локации)</t>
   </si>
   <si>
@@ -97,6 +91,27 @@
   </si>
   <si>
     <t>Цена (руб)</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>Страница "О нас"</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Остаток:</t>
+  </si>
+  <si>
+    <t>Оплачено:</t>
+  </si>
+  <si>
+    <t>(04.04.2026)</t>
+  </si>
+  <si>
+    <t>До:</t>
   </si>
 </sst>
 </file>
@@ -141,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -158,6 +173,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -438,32 +460,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="58.140625" style="6" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B1" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -476,8 +499,11 @@
       <c r="D3">
         <v>4000</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -490,8 +516,11 @@
       <c r="D4">
         <v>4000</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -504,187 +533,218 @@
       <c r="D5">
         <v>4000</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="E5" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6">
+      <c r="B12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17">
         <v>1</v>
       </c>
-      <c r="D6">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
+      <c r="D17">
         <v>2000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17">
-        <v>5</v>
-      </c>
-      <c r="D17">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
-        <v>5</v>
-      </c>
       <c r="B18" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
-        <v>5</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="6" t="s">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C27">
-        <f>SUM(C2:C25)</f>
-        <v>37</v>
-      </c>
-      <c r="D27">
-        <f>SUM(D2:D25)</f>
-        <v>50000</v>
+      <c r="C26">
+        <f>SUM(C2:C24)</f>
+        <v>36</v>
+      </c>
+      <c r="D26">
+        <f>SUM(D2:D24)</f>
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28">
+        <f ca="1">TODAY() - DATE(2026,4,4)</f>
+        <v>4</v>
+      </c>
+      <c r="D28">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29">
+        <f ca="1">(DATE(2026,4,4)+36) - DATE(2026,4,4) - C28</f>
+        <v>32</v>
+      </c>
+      <c r="D29">
+        <f>D26-D28</f>
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="10">
+        <f>DATE(2026,4,4)+36</f>
+        <v>46152</v>
       </c>
     </row>
   </sheetData>

--- a/сайт_записей_на_услуги.xlsx
+++ b/сайт_записей_на_услуги.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>Админ-панель:</t>
   </si>
@@ -112,6 +112,9 @@
   </si>
   <si>
     <t>До:</t>
+  </si>
+  <si>
+    <t>&lt;- выполнено</t>
   </si>
 </sst>
 </file>
@@ -460,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="5" bestFit="1" customWidth="1"/>
@@ -555,6 +558,9 @@
       <c r="D9">
         <v>4000</v>
       </c>
+      <c r="E9" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
@@ -617,7 +623,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>5</v>
       </c>
@@ -631,7 +637,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>7</v>
       </c>
@@ -645,12 +651,12 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>3</v>
       </c>
@@ -664,7 +670,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>5</v>
       </c>
@@ -678,7 +684,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>7</v>
       </c>
@@ -695,7 +701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>18</v>
       </c>
@@ -708,37 +714,44 @@
         <v>49500</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C27" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C28">
         <f ca="1">TODAY() - DATE(2026,4,4)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D28">
         <v>5000</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E28" s="8">
+        <f>SUMIF(E2:E25, "+", D2:D25)</f>
+        <v>15000</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C29">
         <f ca="1">(DATE(2026,4,4)+36) - DATE(2026,4,4) - C28</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D29">
         <f>D26-D28</f>
         <v>44500</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>30</v>
       </c>

--- a/сайт_записей_на_услуги.xlsx
+++ b/сайт_записей_на_услуги.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>Админ-панель:</t>
   </si>
@@ -603,6 +603,9 @@
       <c r="D12">
         <v>2000</v>
       </c>
+      <c r="E12" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -725,14 +728,14 @@
       </c>
       <c r="C28">
         <f ca="1">TODAY() - DATE(2026,4,4)</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D28">
         <v>5000</v>
       </c>
       <c r="E28" s="8">
         <f>SUMIF(E2:E25, "+", D2:D25)</f>
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="F28" t="s">
         <v>31</v>
@@ -744,7 +747,7 @@
       </c>
       <c r="C29">
         <f ca="1">(DATE(2026,4,4)+36) - DATE(2026,4,4) - C28</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D29">
         <f>D26-D28</f>

--- a/сайт_записей_на_услуги.xlsx
+++ b/сайт_записей_на_услуги.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>Админ-панель:</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>Страница "О нас"</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
   <si>
     <t>Остаток:</t>
@@ -537,7 +534,7 @@
         <v>4000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -575,6 +572,9 @@
       <c r="D10">
         <v>2000</v>
       </c>
+      <c r="E10" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -589,6 +589,9 @@
       <c r="D11">
         <v>7000</v>
       </c>
+      <c r="E11" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
@@ -639,6 +642,9 @@
       <c r="D17">
         <v>2000</v>
       </c>
+      <c r="E17" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -719,44 +725,45 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C27" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28">
         <f ca="1">TODAY() - DATE(2026,4,4)</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D28">
-        <v>5000</v>
+        <f>5000+15000</f>
+        <v>20000</v>
       </c>
       <c r="E28" s="8">
         <f>SUMIF(E2:E25, "+", D2:D25)</f>
-        <v>17000</v>
+        <v>32000</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C29">
         <f ca="1">(DATE(2026,4,4)+36) - DATE(2026,4,4) - C28</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D29">
         <f>D26-D28</f>
-        <v>44500</v>
+        <v>29500</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" s="10">
         <f>DATE(2026,4,4)+36</f>

--- a/сайт_записей_на_услуги.xlsx
+++ b/сайт_записей_на_услуги.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C28">
         <f ca="1">TODAY() - DATE(2026,4,4)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D28">
         <f>5000+15000</f>
@@ -754,7 +754,7 @@
       </c>
       <c r="C29">
         <f ca="1">(DATE(2026,4,4)+36) - DATE(2026,4,4) - C28</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D29">
         <f>D26-D28</f>

--- a/сайт_записей_на_услуги.xlsx
+++ b/сайт_записей_на_услуги.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C28">
         <f ca="1">TODAY() - DATE(2026,4,4)</f>
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <f>5000+15000</f>
@@ -754,7 +754,7 @@
       </c>
       <c r="C29">
         <f ca="1">(DATE(2026,4,4)+36) - DATE(2026,4,4) - C28</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D29">
         <f>D26-D28</f>

--- a/сайт_записей_на_услуги.xlsx
+++ b/сайт_записей_на_услуги.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="C28">
         <f ca="1">TODAY() - DATE(2026,4,4)</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D28">
         <f>5000+15000</f>
@@ -754,7 +754,7 @@
       </c>
       <c r="C29">
         <f ca="1">(DATE(2026,4,4)+36) - DATE(2026,4,4) - C28</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <f>D26-D28</f>
